--- a/Directory.xlsx
+++ b/Directory.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pgone.sharepoint.com/sites/POpriority/Shared Documents/Project Eagles/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{56EB1D5E-1C7E-4C5B-96C7-91C2312465AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56DCCECA-0A72-4B0B-95AB-86206C9C1F5A}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{56EB1D5E-1C7E-4C5B-96C7-91C2312465AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C78AF52-61CC-42C6-A28A-1EA525C9BDB9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C0C2A557-DDDC-4852-ACEC-740287787C9B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="107">
   <si>
     <t>Category</t>
   </si>
@@ -74,9 +74,6 @@
     <t>kim.t@pg.com</t>
   </si>
   <si>
-    <t>lim.y@pg.com</t>
-  </si>
-  <si>
     <t>lee.h.31@pg.com</t>
   </si>
   <si>
@@ -98,15 +95,9 @@
     <t>Oral Care</t>
   </si>
   <si>
-    <t>kwak.y@pg.com</t>
-  </si>
-  <si>
     <t>Hair Care</t>
   </si>
   <si>
-    <t>kim.j.47@pg.com</t>
-  </si>
-  <si>
     <t>lee.ka.5@pg.com</t>
   </si>
   <si>
@@ -152,9 +143,6 @@
     <t>gupta.a.26@pg.com</t>
   </si>
   <si>
-    <t>kim.h.13@pg.com</t>
-  </si>
-  <si>
     <t>kim.h.14@pg.com</t>
   </si>
   <si>
@@ -215,9 +203,6 @@
     <t>Kim, Tae Yeon</t>
   </si>
   <si>
-    <t>Lim, Yeji</t>
-  </si>
-  <si>
     <t>Lee, Hannae</t>
   </si>
   <si>
@@ -254,9 +239,6 @@
     <t>Cha, Minjung</t>
   </si>
   <si>
-    <t>Kwak, Yoo Jin</t>
-  </si>
-  <si>
     <t>Cho, Jaehong</t>
   </si>
   <si>
@@ -266,9 +248,6 @@
     <t>Yeon, Jieun</t>
   </si>
   <si>
-    <t>Kim, Junie</t>
-  </si>
-  <si>
     <t>Lee, Katie</t>
   </si>
   <si>
@@ -299,9 +278,6 @@
     <t>Ryu, David</t>
   </si>
   <si>
-    <t>Kim, Haewon</t>
-  </si>
-  <si>
     <t>Kim, Sunyoung</t>
   </si>
   <si>
@@ -357,6 +333,30 @@
   </si>
   <si>
     <t>jeong.h@pg.com</t>
+  </si>
+  <si>
+    <t>Woo, In Gi</t>
+  </si>
+  <si>
+    <t>woo.i@pg.com</t>
+  </si>
+  <si>
+    <t>Kim, Ryunggyung</t>
+  </si>
+  <si>
+    <t>kim.r.2@pg.com</t>
+  </si>
+  <si>
+    <t>Yang, Woosun</t>
+  </si>
+  <si>
+    <t>yang.w@pg.com</t>
+  </si>
+  <si>
+    <t>lim.h.15@pg.com</t>
+  </si>
+  <si>
+    <t>Lim, Hyunsoo</t>
   </si>
 </sst>
 </file>
@@ -781,13 +781,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -801,7 +801,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -815,7 +815,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -829,7 +829,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -843,7 +843,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -851,13 +851,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -868,10 +868,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -879,13 +879,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -896,29 +896,29 @@
         <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>2</v>
@@ -927,661 +927,665 @@
         <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="D40" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1590,7 +1594,7 @@
     <hyperlink ref="C3" r:id="rId2" display="mailto:choi.m@pg.com" xr:uid="{6CF15977-D022-4541-A7FF-37B725AEE1B7}"/>
     <hyperlink ref="C4" r:id="rId3" display="mailto:lee.j.52@pg.com" xr:uid="{B6439F49-F751-458A-8C00-2E10E488B1C1}"/>
     <hyperlink ref="C5" r:id="rId4" display="mailto:kim.t@pg.com" xr:uid="{76EC3C9C-A5CD-4FBD-B74C-F9080FBDD0BE}"/>
-    <hyperlink ref="C7" r:id="rId5" display="mailto:lim.y@pg.com" xr:uid="{3FCAB364-D4A7-469A-8EE2-959FC22A9676}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{3FCAB364-D4A7-469A-8EE2-959FC22A9676}"/>
     <hyperlink ref="C8" r:id="rId6" display="mailto:lee.h.31@pg.com" xr:uid="{20E7EC01-8F86-443B-85C9-CF900BCBFF92}"/>
     <hyperlink ref="C9" r:id="rId7" xr:uid="{62E9C957-8BA9-42F1-90F0-759A28ED6CC0}"/>
     <hyperlink ref="C10" r:id="rId8" display="mailto:chung.i.1@pg.com" xr:uid="{22C525AF-A8F8-49D0-9478-E04EC238DF69}"/>
@@ -1599,55 +1603,65 @@
     <hyperlink ref="C13" r:id="rId11" xr:uid="{43A1672E-7F04-447A-9D62-E981D947FD59}"/>
     <hyperlink ref="C15" r:id="rId12" xr:uid="{68EFA11F-254F-46B0-A048-BF29B903F88F}"/>
     <hyperlink ref="C16" r:id="rId13" display="mailto:lee.h.31@pg.com" xr:uid="{DBBE01FD-8B04-49B2-8933-699554639AC3}"/>
-    <hyperlink ref="C26" r:id="rId14" display="mailto:kwak.y@pg.com" xr:uid="{54A58B30-0309-4F4F-A920-6FF9FE702081}"/>
-    <hyperlink ref="C27" r:id="rId15" display="mailto:park.nw@pg.com" xr:uid="{BEE426F0-39EB-4F7B-B39F-030665223EDD}"/>
-    <hyperlink ref="C29" r:id="rId16" xr:uid="{1C6D6FB8-BED5-4825-B223-360701C63B0C}"/>
-    <hyperlink ref="C28" r:id="rId17" xr:uid="{A4EF762A-0625-4337-B55D-34B5781DAF06}"/>
-    <hyperlink ref="C31" r:id="rId18" xr:uid="{96ADB2ED-206D-4C5F-9760-4744EB8CEB2E}"/>
-    <hyperlink ref="C34" r:id="rId19" display="mailto:kim.j.47@pg.com" xr:uid="{22AD699E-F9EA-4D84-BF94-677F9567B925}"/>
-    <hyperlink ref="C35" r:id="rId20" display="mailto:lee.ka.5@pg.com" xr:uid="{E40E717D-E97E-4D8F-B899-4A9EFD67EBE1}"/>
-    <hyperlink ref="C36" r:id="rId21" xr:uid="{5EF1B23B-7132-45EC-8930-9AD63F7D9C96}"/>
-    <hyperlink ref="C39" r:id="rId22" xr:uid="{29B41A12-538C-4723-967B-25F910B9C4BD}"/>
-    <hyperlink ref="C42" r:id="rId23" display="mailto:kim.y.35@pg.com" xr:uid="{C491F752-C798-49CA-B651-F2B7D0CAE953}"/>
-    <hyperlink ref="C43" r:id="rId24" display="mailto:son.j.3@pg.com" xr:uid="{14BDC554-8BE9-48B1-B689-665B7EC870C2}"/>
-    <hyperlink ref="C44" r:id="rId25" xr:uid="{3EF44BB4-F3EE-4AAA-8778-F4D94870D9E9}"/>
-    <hyperlink ref="C47" r:id="rId26" xr:uid="{2092C641-2B7E-4181-97D9-DD611F536BCE}"/>
-    <hyperlink ref="C48" r:id="rId27" xr:uid="{6136505C-F352-4CA4-BAA9-A692E5068125}"/>
-    <hyperlink ref="C50" r:id="rId28" display="mailto:chung.h.4@pg.com" xr:uid="{3AB59F4A-169D-4510-8A58-C173C177FEDA}"/>
-    <hyperlink ref="C51" r:id="rId29" display="mailto:park.nw@pg.com" xr:uid="{431D908A-8160-4673-88B7-B0511F71E2AC}"/>
-    <hyperlink ref="C52" r:id="rId30" xr:uid="{F152BB97-7D18-4F24-B1B9-A23B37601BAA}"/>
-    <hyperlink ref="C18" r:id="rId31" display="mailto:park.sh.1@pg.com" xr:uid="{FDD611C5-445E-4C69-80E1-933F8CA60444}"/>
-    <hyperlink ref="C19" r:id="rId32" display="mailto:park.nw@pg.com" xr:uid="{8E013356-8336-4EB9-ADAD-59499D4AFE43}"/>
-    <hyperlink ref="C20" r:id="rId33" display="mailto:cho.s.2@pg.com" xr:uid="{F4538FE7-05A0-4196-BC2D-E09280975C58}"/>
-    <hyperlink ref="C21" r:id="rId34" display="mailto:han.s.4@pg.com" xr:uid="{24EAA67D-358B-4176-8630-085C340749BB}"/>
-    <hyperlink ref="C23" r:id="rId35" display="mailto:kim.h.14@pg.com" xr:uid="{39F65C34-7E15-486A-B767-C2B387F3B535}"/>
-    <hyperlink ref="C24" r:id="rId36" display="mailto:cha.m@pg.com" xr:uid="{396593A6-5C4C-42BB-A866-8C3DA8F83A43}"/>
-    <hyperlink ref="C37" r:id="rId37" xr:uid="{7390A43A-3A74-49E9-A578-B030364060E7}"/>
-    <hyperlink ref="C38" r:id="rId38" xr:uid="{746927D8-F7AC-4455-B616-8F06CF56C1C8}"/>
-    <hyperlink ref="C40" r:id="rId39" xr:uid="{A12B11D4-6798-4801-B278-5F15A0AF4052}"/>
-    <hyperlink ref="C45" r:id="rId40" xr:uid="{BB219961-B1EA-4EC3-AE60-1A02EFB7BFD1}"/>
-    <hyperlink ref="C53" r:id="rId41" xr:uid="{D5E63DCD-F758-4D51-A643-1F89EB3E705A}"/>
-    <hyperlink ref="C56" r:id="rId42" xr:uid="{2CBC17AE-F418-43CA-B07C-7EBF8DC3411A}"/>
-    <hyperlink ref="C57" r:id="rId43" display="mailto:cha.m@pg.com" xr:uid="{70F5B87B-7CF5-4284-91C5-1C5EAD470205}"/>
-    <hyperlink ref="C6" r:id="rId44" xr:uid="{49A854C0-A3C1-4347-9E22-751482F3EEA2}"/>
-    <hyperlink ref="C14" r:id="rId45" xr:uid="{CD4008C0-269F-4475-89EE-DF482914CAFF}"/>
-    <hyperlink ref="C30" r:id="rId46" xr:uid="{37DED781-14C0-434C-A699-F9836FA3E5E8}"/>
-    <hyperlink ref="C22" r:id="rId47" xr:uid="{ABD780B9-2BFB-495C-A386-2CAD2446C5BB}"/>
-    <hyperlink ref="C55" r:id="rId48" xr:uid="{E83F5155-9C0C-4B8D-95DE-21C51AF1712B}"/>
-    <hyperlink ref="C46" r:id="rId49" xr:uid="{D661D48C-C749-41B4-A4A4-4890B6F6E076}"/>
-    <hyperlink ref="C54" r:id="rId50" xr:uid="{32CA7C4A-C8E8-4717-B2A6-AB05233913A3}"/>
+    <hyperlink ref="C27" r:id="rId14" display="mailto:park.nw@pg.com" xr:uid="{BEE426F0-39EB-4F7B-B39F-030665223EDD}"/>
+    <hyperlink ref="C29" r:id="rId15" xr:uid="{1C6D6FB8-BED5-4825-B223-360701C63B0C}"/>
+    <hyperlink ref="C28" r:id="rId16" xr:uid="{A4EF762A-0625-4337-B55D-34B5781DAF06}"/>
+    <hyperlink ref="C31" r:id="rId17" xr:uid="{96ADB2ED-206D-4C5F-9760-4744EB8CEB2E}"/>
+    <hyperlink ref="C34" r:id="rId18" xr:uid="{22AD699E-F9EA-4D84-BF94-677F9567B925}"/>
+    <hyperlink ref="C35" r:id="rId19" display="mailto:lee.ka.5@pg.com" xr:uid="{E40E717D-E97E-4D8F-B899-4A9EFD67EBE1}"/>
+    <hyperlink ref="C36" r:id="rId20" xr:uid="{5EF1B23B-7132-45EC-8930-9AD63F7D9C96}"/>
+    <hyperlink ref="C39" r:id="rId21" xr:uid="{29B41A12-538C-4723-967B-25F910B9C4BD}"/>
+    <hyperlink ref="C42" r:id="rId22" display="mailto:kim.y.35@pg.com" xr:uid="{C491F752-C798-49CA-B651-F2B7D0CAE953}"/>
+    <hyperlink ref="C43" r:id="rId23" display="mailto:son.j.3@pg.com" xr:uid="{14BDC554-8BE9-48B1-B689-665B7EC870C2}"/>
+    <hyperlink ref="C44" r:id="rId24" xr:uid="{3EF44BB4-F3EE-4AAA-8778-F4D94870D9E9}"/>
+    <hyperlink ref="C47" r:id="rId25" xr:uid="{2092C641-2B7E-4181-97D9-DD611F536BCE}"/>
+    <hyperlink ref="C50" r:id="rId26" display="mailto:chung.h.4@pg.com" xr:uid="{3AB59F4A-169D-4510-8A58-C173C177FEDA}"/>
+    <hyperlink ref="C51" r:id="rId27" display="mailto:park.nw@pg.com" xr:uid="{431D908A-8160-4673-88B7-B0511F71E2AC}"/>
+    <hyperlink ref="C52" r:id="rId28" xr:uid="{F152BB97-7D18-4F24-B1B9-A23B37601BAA}"/>
+    <hyperlink ref="C18" r:id="rId29" display="mailto:park.sh.1@pg.com" xr:uid="{FDD611C5-445E-4C69-80E1-933F8CA60444}"/>
+    <hyperlink ref="C19" r:id="rId30" display="mailto:park.nw@pg.com" xr:uid="{8E013356-8336-4EB9-ADAD-59499D4AFE43}"/>
+    <hyperlink ref="C20" r:id="rId31" display="mailto:cho.s.2@pg.com" xr:uid="{F4538FE7-05A0-4196-BC2D-E09280975C58}"/>
+    <hyperlink ref="C21" r:id="rId32" display="mailto:han.s.4@pg.com" xr:uid="{24EAA67D-358B-4176-8630-085C340749BB}"/>
+    <hyperlink ref="C23" r:id="rId33" display="mailto:kim.h.14@pg.com" xr:uid="{39F65C34-7E15-486A-B767-C2B387F3B535}"/>
+    <hyperlink ref="C24" r:id="rId34" display="mailto:cha.m@pg.com" xr:uid="{396593A6-5C4C-42BB-A866-8C3DA8F83A43}"/>
+    <hyperlink ref="C37" r:id="rId35" xr:uid="{7390A43A-3A74-49E9-A578-B030364060E7}"/>
+    <hyperlink ref="C38" r:id="rId36" xr:uid="{746927D8-F7AC-4455-B616-8F06CF56C1C8}"/>
+    <hyperlink ref="C40" r:id="rId37" xr:uid="{A12B11D4-6798-4801-B278-5F15A0AF4052}"/>
+    <hyperlink ref="C45" r:id="rId38" xr:uid="{BB219961-B1EA-4EC3-AE60-1A02EFB7BFD1}"/>
+    <hyperlink ref="C53" r:id="rId39" xr:uid="{D5E63DCD-F758-4D51-A643-1F89EB3E705A}"/>
+    <hyperlink ref="C56" r:id="rId40" xr:uid="{2CBC17AE-F418-43CA-B07C-7EBF8DC3411A}"/>
+    <hyperlink ref="C57" r:id="rId41" display="mailto:cha.m@pg.com" xr:uid="{70F5B87B-7CF5-4284-91C5-1C5EAD470205}"/>
+    <hyperlink ref="C6" r:id="rId42" xr:uid="{49A854C0-A3C1-4347-9E22-751482F3EEA2}"/>
+    <hyperlink ref="C14" r:id="rId43" xr:uid="{CD4008C0-269F-4475-89EE-DF482914CAFF}"/>
+    <hyperlink ref="C30" r:id="rId44" xr:uid="{37DED781-14C0-434C-A699-F9836FA3E5E8}"/>
+    <hyperlink ref="C22" r:id="rId45" xr:uid="{ABD780B9-2BFB-495C-A386-2CAD2446C5BB}"/>
+    <hyperlink ref="C55" r:id="rId46" xr:uid="{E83F5155-9C0C-4B8D-95DE-21C51AF1712B}"/>
+    <hyperlink ref="C46" r:id="rId47" xr:uid="{D661D48C-C749-41B4-A4A4-4890B6F6E076}"/>
+    <hyperlink ref="C54" r:id="rId48" xr:uid="{32CA7C4A-C8E8-4717-B2A6-AB05233913A3}"/>
+    <hyperlink ref="C26" r:id="rId49" display="mailto:park.sh.1@pg.com" xr:uid="{D76E9F96-4368-4E59-88AD-75AC72E215C5}"/>
+    <hyperlink ref="C32" r:id="rId50" xr:uid="{97B09D4D-D2A6-4AE7-8DFC-2709F3D5C1A0}"/>
+    <hyperlink ref="C48" r:id="rId51" xr:uid="{230AE0DD-2EF7-4AFA-8321-DC1FBFFF1C42}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;"Calibri"&amp;10&amp;K000000 Business Use&amp;1#_x000D_</oddHeader>
   </headerFooter>
   <customProperties>
-    <customPr name="_pios_id" r:id="rId51"/>
+    <customPr name="_pios_id" r:id="rId52"/>
   </customProperties>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6c0e7a184c0233f586ea7baba2e967b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6204f9fca8cd82ddbd42930875406446" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
@@ -1870,15 +1884,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1891,6 +1896,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B381B43-2BC5-4F31-BCB9-8B232C6A84C3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE5BD9FE-090E-4AE2-942B-DE48A93E9A44}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1905,14 +1918,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B381B43-2BC5-4F31-BCB9-8B232C6A84C3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Directory.xlsx
+++ b/Directory.xlsx
@@ -1662,8 +1662,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6c0e7a184c0233f586ea7baba2e967b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6204f9fca8cd82ddbd42930875406446" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b8c77ac32eabc1baceb6fb4a0eaa7e9a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dfa206d4ab44e8502d05ea0aeb673323" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
     <xsd:import namespace="96d24a6b-8465-4498-bb54-acea15c87a74"/>
     <xsd:element name="properties">
@@ -1904,22 +1904,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE5BD9FE-090E-4AE2-942B-DE48A93E9A44}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="57147975-5687-4135-8263-39f5df548c17"/>
-    <ds:schemaRef ds:uri="96d24a6b-8465-4498-bb54-acea15c87a74"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B76C8556-894B-49B7-B0E0-C63DB45BD8E5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Directory.xlsx
+++ b/Directory.xlsx
@@ -1662,8 +1662,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b8c77ac32eabc1baceb6fb4a0eaa7e9a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dfa206d4ab44e8502d05ea0aeb673323" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d9416936a3b57ab26e55784844af5429">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9218ed845bf90baf0025c167a9057e7b" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
     <xsd:import namespace="96d24a6b-8465-4498-bb54-acea15c87a74"/>
     <xsd:element name="properties">
@@ -1684,6 +1684,8 @@
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:i0f84bba906045b4af568ee102a52dcb" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1743,6 +1745,11 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="96d24a6b-8465-4498-bb54-acea15c87a74" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -1782,6 +1789,13 @@
             </xsd:sequence>
           </xsd:extension>
         </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="i0f84bba906045b4af568ee102a52dcb" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="i0f84bba906045b4af568ee102a52dcb" ma:taxonomyFieldName="RevIMBCS" ma:displayName="Retention Policy" ma:indexed="true" ma:default="5;#Daily Work Documents [Standard]|c1df7c93-bf29-4bb4-a9f3-5b7aacc5e62b" ma:fieldId="{20f84bba-9060-45b4-af56-8ee102a52dcb}" ma:sspId="c81b625c-6132-4315-8b99-2d7d4df07560" ma:termSetId="1d8deb5c-7ccc-4e04-a1de-f52ad8333138" ma:anchorId="00000000-0000-0000-0000-000000000000" ma:open="false" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
@@ -1890,7 +1904,17 @@
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="57147975-5687-4135-8263-39f5df548c17">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="96d24a6b-8465-4498-bb54-acea15c87a74" xsi:nil="true"/>
+    <TaxCatchAll xmlns="96d24a6b-8465-4498-bb54-acea15c87a74">
+      <Value>5</Value>
+    </TaxCatchAll>
+    <i0f84bba906045b4af568ee102a52dcb xmlns="96d24a6b-8465-4498-bb54-acea15c87a74">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Daily Work Documents [Standard]</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">c1df7c93-bf29-4bb4-a9f3-5b7aacc5e62b</TermId>
+        </TermInfo>
+      </Terms>
+    </i0f84bba906045b4af568ee102a52dcb>
   </documentManagement>
 </p:properties>
 </file>
@@ -1904,7 +1928,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B76C8556-894B-49B7-B0E0-C63DB45BD8E5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86478BD8-7206-4801-B18B-6A81F400CF52}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Directory.xlsx
+++ b/Directory.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pgone.sharepoint.com/sites/POpriority/Shared Documents/Project Eagles/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{56EB1D5E-1C7E-4C5B-96C7-91C2312465AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C78AF52-61CC-42C6-A28A-1EA525C9BDB9}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{56EB1D5E-1C7E-4C5B-96C7-91C2312465AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{472DE7DC-723B-469D-B79A-5E9C368CECD1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C0C2A557-DDDC-4852-ACEC-740287787C9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentManualCount="8"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -341,12 +341,6 @@
     <t>woo.i@pg.com</t>
   </si>
   <si>
-    <t>Kim, Ryunggyung</t>
-  </si>
-  <si>
-    <t>kim.r.2@pg.com</t>
-  </si>
-  <si>
     <t>Yang, Woosun</t>
   </si>
   <si>
@@ -357,6 +351,12 @@
   </si>
   <si>
     <t>Lim, Hyunsoo</t>
+  </si>
+  <si>
+    <t>Yoo, Kelly</t>
+  </si>
+  <si>
+    <t>yoo.y@pg.com</t>
   </si>
 </sst>
 </file>
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1428,10 +1428,10 @@
         <v>4</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1442,10 +1442,10 @@
         <v>40</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1607,40 +1607,40 @@
     <hyperlink ref="C29" r:id="rId15" xr:uid="{1C6D6FB8-BED5-4825-B223-360701C63B0C}"/>
     <hyperlink ref="C28" r:id="rId16" xr:uid="{A4EF762A-0625-4337-B55D-34B5781DAF06}"/>
     <hyperlink ref="C31" r:id="rId17" xr:uid="{96ADB2ED-206D-4C5F-9760-4744EB8CEB2E}"/>
-    <hyperlink ref="C34" r:id="rId18" xr:uid="{22AD699E-F9EA-4D84-BF94-677F9567B925}"/>
-    <hyperlink ref="C35" r:id="rId19" display="mailto:lee.ka.5@pg.com" xr:uid="{E40E717D-E97E-4D8F-B899-4A9EFD67EBE1}"/>
-    <hyperlink ref="C36" r:id="rId20" xr:uid="{5EF1B23B-7132-45EC-8930-9AD63F7D9C96}"/>
-    <hyperlink ref="C39" r:id="rId21" xr:uid="{29B41A12-538C-4723-967B-25F910B9C4BD}"/>
-    <hyperlink ref="C42" r:id="rId22" display="mailto:kim.y.35@pg.com" xr:uid="{C491F752-C798-49CA-B651-F2B7D0CAE953}"/>
-    <hyperlink ref="C43" r:id="rId23" display="mailto:son.j.3@pg.com" xr:uid="{14BDC554-8BE9-48B1-B689-665B7EC870C2}"/>
-    <hyperlink ref="C44" r:id="rId24" xr:uid="{3EF44BB4-F3EE-4AAA-8778-F4D94870D9E9}"/>
-    <hyperlink ref="C47" r:id="rId25" xr:uid="{2092C641-2B7E-4181-97D9-DD611F536BCE}"/>
-    <hyperlink ref="C50" r:id="rId26" display="mailto:chung.h.4@pg.com" xr:uid="{3AB59F4A-169D-4510-8A58-C173C177FEDA}"/>
-    <hyperlink ref="C51" r:id="rId27" display="mailto:park.nw@pg.com" xr:uid="{431D908A-8160-4673-88B7-B0511F71E2AC}"/>
-    <hyperlink ref="C52" r:id="rId28" xr:uid="{F152BB97-7D18-4F24-B1B9-A23B37601BAA}"/>
-    <hyperlink ref="C18" r:id="rId29" display="mailto:park.sh.1@pg.com" xr:uid="{FDD611C5-445E-4C69-80E1-933F8CA60444}"/>
-    <hyperlink ref="C19" r:id="rId30" display="mailto:park.nw@pg.com" xr:uid="{8E013356-8336-4EB9-ADAD-59499D4AFE43}"/>
-    <hyperlink ref="C20" r:id="rId31" display="mailto:cho.s.2@pg.com" xr:uid="{F4538FE7-05A0-4196-BC2D-E09280975C58}"/>
-    <hyperlink ref="C21" r:id="rId32" display="mailto:han.s.4@pg.com" xr:uid="{24EAA67D-358B-4176-8630-085C340749BB}"/>
-    <hyperlink ref="C23" r:id="rId33" display="mailto:kim.h.14@pg.com" xr:uid="{39F65C34-7E15-486A-B767-C2B387F3B535}"/>
-    <hyperlink ref="C24" r:id="rId34" display="mailto:cha.m@pg.com" xr:uid="{396593A6-5C4C-42BB-A866-8C3DA8F83A43}"/>
-    <hyperlink ref="C37" r:id="rId35" xr:uid="{7390A43A-3A74-49E9-A578-B030364060E7}"/>
-    <hyperlink ref="C38" r:id="rId36" xr:uid="{746927D8-F7AC-4455-B616-8F06CF56C1C8}"/>
-    <hyperlink ref="C40" r:id="rId37" xr:uid="{A12B11D4-6798-4801-B278-5F15A0AF4052}"/>
-    <hyperlink ref="C45" r:id="rId38" xr:uid="{BB219961-B1EA-4EC3-AE60-1A02EFB7BFD1}"/>
-    <hyperlink ref="C53" r:id="rId39" xr:uid="{D5E63DCD-F758-4D51-A643-1F89EB3E705A}"/>
-    <hyperlink ref="C56" r:id="rId40" xr:uid="{2CBC17AE-F418-43CA-B07C-7EBF8DC3411A}"/>
-    <hyperlink ref="C57" r:id="rId41" display="mailto:cha.m@pg.com" xr:uid="{70F5B87B-7CF5-4284-91C5-1C5EAD470205}"/>
-    <hyperlink ref="C6" r:id="rId42" xr:uid="{49A854C0-A3C1-4347-9E22-751482F3EEA2}"/>
-    <hyperlink ref="C14" r:id="rId43" xr:uid="{CD4008C0-269F-4475-89EE-DF482914CAFF}"/>
-    <hyperlink ref="C30" r:id="rId44" xr:uid="{37DED781-14C0-434C-A699-F9836FA3E5E8}"/>
-    <hyperlink ref="C22" r:id="rId45" xr:uid="{ABD780B9-2BFB-495C-A386-2CAD2446C5BB}"/>
-    <hyperlink ref="C55" r:id="rId46" xr:uid="{E83F5155-9C0C-4B8D-95DE-21C51AF1712B}"/>
-    <hyperlink ref="C46" r:id="rId47" xr:uid="{D661D48C-C749-41B4-A4A4-4890B6F6E076}"/>
-    <hyperlink ref="C54" r:id="rId48" xr:uid="{32CA7C4A-C8E8-4717-B2A6-AB05233913A3}"/>
-    <hyperlink ref="C26" r:id="rId49" display="mailto:park.sh.1@pg.com" xr:uid="{D76E9F96-4368-4E59-88AD-75AC72E215C5}"/>
-    <hyperlink ref="C32" r:id="rId50" xr:uid="{97B09D4D-D2A6-4AE7-8DFC-2709F3D5C1A0}"/>
-    <hyperlink ref="C48" r:id="rId51" xr:uid="{230AE0DD-2EF7-4AFA-8321-DC1FBFFF1C42}"/>
+    <hyperlink ref="C35" r:id="rId18" display="mailto:lee.ka.5@pg.com" xr:uid="{E40E717D-E97E-4D8F-B899-4A9EFD67EBE1}"/>
+    <hyperlink ref="C36" r:id="rId19" xr:uid="{5EF1B23B-7132-45EC-8930-9AD63F7D9C96}"/>
+    <hyperlink ref="C39" r:id="rId20" xr:uid="{29B41A12-538C-4723-967B-25F910B9C4BD}"/>
+    <hyperlink ref="C42" r:id="rId21" display="mailto:kim.y.35@pg.com" xr:uid="{C491F752-C798-49CA-B651-F2B7D0CAE953}"/>
+    <hyperlink ref="C43" r:id="rId22" display="mailto:son.j.3@pg.com" xr:uid="{14BDC554-8BE9-48B1-B689-665B7EC870C2}"/>
+    <hyperlink ref="C44" r:id="rId23" xr:uid="{3EF44BB4-F3EE-4AAA-8778-F4D94870D9E9}"/>
+    <hyperlink ref="C47" r:id="rId24" xr:uid="{2092C641-2B7E-4181-97D9-DD611F536BCE}"/>
+    <hyperlink ref="C50" r:id="rId25" display="mailto:chung.h.4@pg.com" xr:uid="{3AB59F4A-169D-4510-8A58-C173C177FEDA}"/>
+    <hyperlink ref="C51" r:id="rId26" display="mailto:park.nw@pg.com" xr:uid="{431D908A-8160-4673-88B7-B0511F71E2AC}"/>
+    <hyperlink ref="C52" r:id="rId27" xr:uid="{F152BB97-7D18-4F24-B1B9-A23B37601BAA}"/>
+    <hyperlink ref="C18" r:id="rId28" display="mailto:park.sh.1@pg.com" xr:uid="{FDD611C5-445E-4C69-80E1-933F8CA60444}"/>
+    <hyperlink ref="C19" r:id="rId29" display="mailto:park.nw@pg.com" xr:uid="{8E013356-8336-4EB9-ADAD-59499D4AFE43}"/>
+    <hyperlink ref="C20" r:id="rId30" display="mailto:cho.s.2@pg.com" xr:uid="{F4538FE7-05A0-4196-BC2D-E09280975C58}"/>
+    <hyperlink ref="C21" r:id="rId31" display="mailto:han.s.4@pg.com" xr:uid="{24EAA67D-358B-4176-8630-085C340749BB}"/>
+    <hyperlink ref="C23" r:id="rId32" display="mailto:kim.h.14@pg.com" xr:uid="{39F65C34-7E15-486A-B767-C2B387F3B535}"/>
+    <hyperlink ref="C24" r:id="rId33" display="mailto:cha.m@pg.com" xr:uid="{396593A6-5C4C-42BB-A866-8C3DA8F83A43}"/>
+    <hyperlink ref="C37" r:id="rId34" xr:uid="{7390A43A-3A74-49E9-A578-B030364060E7}"/>
+    <hyperlink ref="C38" r:id="rId35" xr:uid="{746927D8-F7AC-4455-B616-8F06CF56C1C8}"/>
+    <hyperlink ref="C40" r:id="rId36" xr:uid="{A12B11D4-6798-4801-B278-5F15A0AF4052}"/>
+    <hyperlink ref="C45" r:id="rId37" xr:uid="{BB219961-B1EA-4EC3-AE60-1A02EFB7BFD1}"/>
+    <hyperlink ref="C53" r:id="rId38" xr:uid="{D5E63DCD-F758-4D51-A643-1F89EB3E705A}"/>
+    <hyperlink ref="C56" r:id="rId39" xr:uid="{2CBC17AE-F418-43CA-B07C-7EBF8DC3411A}"/>
+    <hyperlink ref="C57" r:id="rId40" display="mailto:cha.m@pg.com" xr:uid="{70F5B87B-7CF5-4284-91C5-1C5EAD470205}"/>
+    <hyperlink ref="C6" r:id="rId41" xr:uid="{49A854C0-A3C1-4347-9E22-751482F3EEA2}"/>
+    <hyperlink ref="C14" r:id="rId42" xr:uid="{CD4008C0-269F-4475-89EE-DF482914CAFF}"/>
+    <hyperlink ref="C30" r:id="rId43" xr:uid="{37DED781-14C0-434C-A699-F9836FA3E5E8}"/>
+    <hyperlink ref="C22" r:id="rId44" xr:uid="{ABD780B9-2BFB-495C-A386-2CAD2446C5BB}"/>
+    <hyperlink ref="C55" r:id="rId45" xr:uid="{E83F5155-9C0C-4B8D-95DE-21C51AF1712B}"/>
+    <hyperlink ref="C46" r:id="rId46" xr:uid="{D661D48C-C749-41B4-A4A4-4890B6F6E076}"/>
+    <hyperlink ref="C54" r:id="rId47" xr:uid="{32CA7C4A-C8E8-4717-B2A6-AB05233913A3}"/>
+    <hyperlink ref="C26" r:id="rId48" display="mailto:park.sh.1@pg.com" xr:uid="{D76E9F96-4368-4E59-88AD-75AC72E215C5}"/>
+    <hyperlink ref="C32" r:id="rId49" xr:uid="{97B09D4D-D2A6-4AE7-8DFC-2709F3D5C1A0}"/>
+    <hyperlink ref="C48" r:id="rId50" xr:uid="{230AE0DD-2EF7-4AFA-8321-DC1FBFFF1C42}"/>
+    <hyperlink ref="C34" r:id="rId51" xr:uid="{9E84606F-0F10-4DA6-B332-5BF6DD3AAF96}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
@@ -1653,17 +1653,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d9416936a3b57ab26e55784844af5429">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9218ed845bf90baf0025c167a9057e7b" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="40a43f087754221fa183e12f61eae985">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="025949cc6f7c326f5f6f4d123f9252f7" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
     <xsd:import namespace="96d24a6b-8465-4498-bb54-acea15c87a74"/>
     <xsd:element name="properties">
@@ -1898,6 +1889,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1920,15 +1920,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85F56190-11C0-4BEA-A26A-C32BC0286BF9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B381B43-2BC5-4F31-BCB9-8B232C6A84C3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86478BD8-7206-4801-B18B-6A81F400CF52}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
